--- a/src/test/resources/datatest/SetProductData.xlsx
+++ b/src/test/resources/datatest/SetProductData.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Product Name</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Asus</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>3000</t>
   </si>
   <si>
@@ -84,6 +81,15 @@
   </si>
   <si>
     <t>laptop_asus.webp</t>
+  </si>
+  <si>
+    <t>Color</t>
+  </si>
+  <si>
+    <t>Aqua</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -414,21 +420,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="4.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="9.69921875" customWidth="1"/>
-    <col min="7" max="7" width="5.59765625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.8984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.09765625" customWidth="1"/>
+    <col min="6" max="7" width="9.69921875" customWidth="1"/>
+    <col min="8" max="8" width="5.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.8984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -442,25 +449,28 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -473,23 +483,26 @@
       <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" t="s">
         <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
